--- a/output/pdf_financials_xlsx/PAT.xlsx
+++ b/output/pdf_financials_xlsx/PAT.xlsx
@@ -4780,7 +4780,7 @@
         <v>0.653431</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.993669</v>
+        <v>1.440173</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>1.245953</v>
@@ -8071,7 +8071,11 @@
           <t>Warrants Reserve (note 4)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -39627,7 +39631,7 @@
         </is>
       </c>
       <c r="E410" s="5" t="n">
-        <v>0.009594</v>
+        <v>-0.009594</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PAT.xlsx
+++ b/output/pdf_financials_xlsx/PAT.xlsx
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002717</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.004472</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.010767</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>-0.039085</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.323544</v>
+        <v>0.320827</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.761548</v>
@@ -1701,10 +1701,10 @@
         <v>-0.294999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.986398</v>
+        <v>-0.99087</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.267113</v>
+        <v>-0.27788</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.240145</v>
@@ -1766,7 +1766,7 @@
         <v>-0.039085</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.323544</v>
+        <v>0.320827</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.760803</v>
@@ -1793,10 +1793,10 @@
         <v>-0.294999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.986398</v>
+        <v>-0.99087</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.267113</v>
+        <v>-0.27788</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.240145</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>10.28471923991797</v>
+        <v>10.19835206211571</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-19.00773897740367</v>
@@ -1994,10 +1994,10 @@
         <v>0.655649</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.023252</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.073812</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.05256</v>
@@ -2018,7 +2018,7 @@
         <v>0.239821</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.303002</v>
       </c>
     </row>
     <row r="35">
@@ -2086,10 +2086,10 @@
         <v>0.655649</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.023252</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.073812</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.05256</v>
@@ -2110,7 +2110,7 @@
         <v>0.239821</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.303002</v>
       </c>
     </row>
     <row r="37">
@@ -2638,10 +2638,10 @@
         <v>0.20173</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.316336</v>
+        <v>0.293084</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.09216299999999999</v>
+        <v>0.018351</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.043216</v>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.303002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -30882,7 +30882,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -32342,7 +32342,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -35401,7 +35401,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">

--- a/output/pdf_financials_xlsx/PAT.xlsx
+++ b/output/pdf_financials_xlsx/PAT.xlsx
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-0.610975</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
         <v>-0.993997</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0.182521</v>
+        <v>-0.428454</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-0.041778</v>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003622</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.002887</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.000326</v>
@@ -5157,19 +5157,19 @@
         <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.002285</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004977</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.001315</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.015474</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.017035</v>
       </c>
     </row>
     <row r="102">
@@ -5363,7 +5363,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.032804</v>
+        <v>0.029182</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.535138</v>
@@ -6797,7 +6797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q416"/>
+  <dimension ref="A1:Q424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14435,7 +14435,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -14869,7 +14873,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -16143,11 +16151,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -17826,7 +17830,11 @@
           <t>Issuance of shares pursuant to private placement</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -18954,7 +18962,11 @@
           <t>Issuance of shares pursuant to private placement (note 5(a))</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -27996,7 +28008,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -28978,7 +28994,11 @@
           <t>(Increase) Decrease in GST recoverable</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E277" s="5" t="n">
         <v>-0.000135</v>
       </c>
@@ -29549,7 +29569,11 @@
           <t>Decrease (Increase) in GST recoverable</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E284" s="5" t="n">
         <v>-0.003487</v>
       </c>
@@ -30271,28 +30295,26 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS USED IN OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Consulting fees (note 6) $</t>
+          <t>Increase in GST recoverable</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="n">
+        <v>-0.000135</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30339,64 +30361,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O293" s="5" t="n">
-        <v>0.06660000000000001</v>
-      </c>
-      <c r="P293" s="5" t="n">
-        <v>0.1416</v>
-      </c>
-      <c r="Q293" s="5" t="n">
-        <v>0.1446</v>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
+          <t>Proceeds from share issuance</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="n">
+        <v>0.1</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G294" s="5" t="n">
-        <v>0.002154</v>
-      </c>
-      <c r="H294" s="5" t="n">
-        <v>0.021882</v>
-      </c>
-      <c r="I294" s="5" t="n">
-        <v>0.017024</v>
-      </c>
-      <c r="J294" s="5" t="n">
-        <v>0.049076</v>
-      </c>
-      <c r="K294" s="5" t="n">
-        <v>0.032275</v>
-      </c>
-      <c r="L294" s="5" t="n">
-        <v>0.046103</v>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
@@ -30408,41 +30446,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O294" s="5" t="n">
-        <v>0.015832</v>
-      </c>
-      <c r="P294" s="5" t="n">
-        <v>0.027226</v>
-      </c>
-      <c r="Q294" s="5" t="n">
-        <v>0.009568</v>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Increase in GST recoverable</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="n">
+        <v>-0.003487</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -30454,14 +30496,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H295" s="5" t="n">
-        <v>0.079411</v>
-      </c>
-      <c r="I295" s="5" t="n">
-        <v>0.060022</v>
-      </c>
-      <c r="J295" s="5" t="n">
-        <v>9.8e-05</v>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -30473,8 +30521,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M295" s="5" t="n">
-        <v>0.4431</v>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
@@ -30486,8 +30536,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P295" s="5" t="n">
-        <v>0.026066</v>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
@@ -30498,91 +30550,111 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Increase in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F296" s="5" t="n">
-        <v>0.006787</v>
-      </c>
-      <c r="G296" s="5" t="n">
-        <v>0.029333</v>
-      </c>
-      <c r="H296" s="5" t="n">
-        <v>0.060039</v>
-      </c>
-      <c r="I296" s="5" t="n">
-        <v>0.182546</v>
-      </c>
-      <c r="J296" s="5" t="n">
-        <v>0.106244</v>
-      </c>
-      <c r="K296" s="5" t="n">
-        <v>0.01905</v>
-      </c>
-      <c r="L296" s="5" t="n">
-        <v>0.025405</v>
-      </c>
-      <c r="M296" s="5" t="n">
-        <v>0.003609</v>
-      </c>
-      <c r="N296" s="5" t="n">
-        <v>0.006688</v>
-      </c>
-      <c r="O296" s="5" t="n">
-        <v>0.004057</v>
-      </c>
-      <c r="P296" s="5" t="n">
-        <v>0.020671</v>
-      </c>
-      <c r="Q296" s="5" t="n">
-        <v>0.023657</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>0.025003</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Professional fees (note 6)</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="n">
+        <v>0.06497699999999999</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -30619,43 +30691,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M297" s="5" t="n">
-        <v>0.064606</v>
-      </c>
-      <c r="N297" s="5" t="n">
-        <v>0.071604</v>
-      </c>
-      <c r="O297" s="5" t="n">
-        <v>0.050254</v>
-      </c>
-      <c r="P297" s="5" t="n">
-        <v>0.102717</v>
-      </c>
-      <c r="Q297" s="5" t="n">
-        <v>6.232e-05</v>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Shareholder information</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net increase in cash</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="n">
+        <v>0.06304899999999999</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -30692,17 +30776,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M298" s="5" t="n">
-        <v>0.007144</v>
-      </c>
-      <c r="N298" s="5" t="n">
-        <v>0.014529</v>
-      </c>
-      <c r="O298" s="5" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="P298" s="5" t="n">
-        <v>0.0041</v>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
@@ -30713,22 +30805,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Net loss from operations</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -30771,43 +30863,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M299" s="5" t="n">
-        <v>-0.664621</v>
-      </c>
-      <c r="N299" s="5" t="n">
-        <v>-0.180218</v>
-      </c>
-      <c r="O299" s="5" t="n">
-        <v>-0.690011</v>
-      </c>
-      <c r="P299" s="5" t="n">
-        <v>-0.32238</v>
-      </c>
-      <c r="Q299" s="5" t="n">
-        <v>-0.240145</v>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (note 3)</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="n">
+        <v>0.06304899999999999</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -30849,14 +30953,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N300" s="5" t="n">
-        <v>-0.114781</v>
-      </c>
-      <c r="O300" s="5" t="n">
-        <v>-0.300859</v>
-      </c>
-      <c r="P300" s="5" t="n">
-        <v>-0.0215</v>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
@@ -30872,17 +30982,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Consulting fees (note 6) $</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -30936,15 +31046,13 @@
         </is>
       </c>
       <c r="O301" s="5" t="n">
-        <v>0.004472</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="P301" s="5" t="n">
-        <v>0.010767</v>
-      </c>
-      <c r="Q301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1416</v>
+      </c>
+      <c r="Q301" s="5" t="n">
+        <v>0.1446</v>
       </c>
     </row>
     <row r="302">
@@ -30955,15 +31063,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Settlement of flow-through shares (note 8)</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>Listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -30974,35 +31086,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G302" s="5" t="n">
+        <v>0.002154</v>
+      </c>
+      <c r="H302" s="5" t="n">
+        <v>0.021882</v>
+      </c>
+      <c r="I302" s="5" t="n">
+        <v>0.017024</v>
+      </c>
+      <c r="J302" s="5" t="n">
+        <v>0.049076</v>
+      </c>
+      <c r="K302" s="5" t="n">
+        <v>0.032275</v>
+      </c>
+      <c r="L302" s="5" t="n">
+        <v>0.046103</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
@@ -31014,18 +31114,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O302" s="5" t="n">
+        <v>0.015832</v>
       </c>
       <c r="P302" s="5" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="Q302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027226</v>
+      </c>
+      <c r="Q302" s="5" t="n">
+        <v>0.009568</v>
       </c>
     </row>
     <row r="303">
@@ -31036,17 +31132,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -31064,20 +31160,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H303" s="5" t="n">
+        <v>0.079411</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>0.060022</v>
+      </c>
+      <c r="J303" s="5" t="n">
+        <v>9.8e-05</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -31089,22 +31179,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N303" s="5" t="n">
-        <v>-0.294999</v>
-      </c>
-      <c r="O303" s="5" t="n">
-        <v>-0.986398</v>
+      <c r="M303" s="5" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P303" s="5" t="n">
-        <v>-0.267113</v>
-      </c>
-      <c r="Q303" s="5" t="n">
-        <v>-0.240145</v>
+        <v>0.026066</v>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -31115,17 +31209,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding –</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -31133,57 +31227,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F304" s="5" t="n">
+        <v>0.006787</v>
+      </c>
+      <c r="G304" s="5" t="n">
+        <v>0.029333</v>
+      </c>
+      <c r="H304" s="5" t="n">
+        <v>0.060039</v>
+      </c>
+      <c r="I304" s="5" t="n">
+        <v>0.182546</v>
+      </c>
+      <c r="J304" s="5" t="n">
+        <v>0.106244</v>
+      </c>
+      <c r="K304" s="5" t="n">
+        <v>0.01905</v>
+      </c>
+      <c r="L304" s="5" t="n">
+        <v>0.025405</v>
+      </c>
+      <c r="M304" s="5" t="n">
+        <v>0.003609</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>42.257899</v>
+        <v>0.006688</v>
       </c>
       <c r="O304" s="5" t="n">
-        <v>4.948485</v>
+        <v>0.004057</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>5.426321</v>
+        <v>0.020671</v>
       </c>
       <c r="Q304" s="5" t="n">
-        <v>6.196736</v>
+        <v>0.023657</v>
       </c>
     </row>
     <row r="305">
@@ -31194,17 +31272,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>basic and diluted</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Basic and fully diluted loss per share $</t>
+          <t>Professional fees (note 6)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -31247,22 +31325,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M305" s="5" t="n">
+        <v>0.064606</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.071604</v>
       </c>
       <c r="O305" s="5" t="n">
-        <v>-2e-07</v>
+        <v>0.050254</v>
       </c>
       <c r="P305" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.102717</v>
       </c>
       <c r="Q305" s="5" t="n">
-        <v>-4e-08</v>
+        <v>6.232e-05</v>
       </c>
     </row>
     <row r="306">
@@ -31278,7 +31354,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Shareholder information</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -31322,23 +31398,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M306" s="5" t="n">
+        <v>0.007144</v>
+      </c>
+      <c r="N306" s="5" t="n">
+        <v>0.014529</v>
       </c>
       <c r="O306" s="5" t="n">
-        <v>0.551368</v>
-      </c>
-      <c r="P306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0019</v>
+      </c>
+      <c r="P306" s="5" t="n">
+        <v>0.0041</v>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
@@ -31354,15 +31424,19 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Settlement of flow through shares</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
+          <t>Net loss from operations</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -31403,28 +31477,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M307" s="5" t="n">
+        <v>-0.664621</v>
+      </c>
+      <c r="N307" s="5" t="n">
+        <v>-0.180218</v>
+      </c>
+      <c r="O307" s="5" t="n">
+        <v>-0.690011</v>
       </c>
       <c r="P307" s="5" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="Q307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.32238</v>
+      </c>
+      <c r="Q307" s="5" t="n">
+        <v>-0.240145</v>
       </c>
     </row>
     <row r="308">
@@ -31435,19 +31501,15 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Listing and filing fees $</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Impairment of exploration and evaluation assets (note 3)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -31488,19 +31550,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M308" s="5" t="n">
-        <v>0.013974</v>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N308" s="5" t="n">
-        <v>0.012903</v>
+        <v>-0.114781</v>
       </c>
       <c r="O308" s="5" t="n">
-        <v>0.015832</v>
-      </c>
-      <c r="P308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.300859</v>
+      </c>
+      <c r="P308" s="5" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
@@ -31516,17 +31578,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 6)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -31569,19 +31631,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M309" s="5" t="n">
-        <v>0.132188</v>
-      </c>
-      <c r="N309" s="5" t="n">
-        <v>0.074494</v>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O309" s="5" t="n">
-        <v>0.06660000000000001</v>
-      </c>
-      <c r="P309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004472</v>
+      </c>
+      <c r="P309" s="5" t="n">
+        <v>0.010767</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
@@ -31597,12 +31661,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 4)</t>
+          <t>Settlement of flow-through shares (note 8)</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -31656,13 +31720,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O310" s="5" t="n">
-        <v>0.551368</v>
-      </c>
-      <c r="P310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P310" s="5" t="n">
+        <v>0.066</v>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
@@ -31683,10 +31747,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -31733,22 +31801,16 @@
         </is>
       </c>
       <c r="N311" s="5" t="n">
-        <v>-0.114781</v>
-      </c>
-      <c r="O311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.294999</v>
+      </c>
+      <c r="O311" s="5" t="n">
+        <v>-0.986398</v>
+      </c>
+      <c r="P311" s="5" t="n">
+        <v>-0.267113</v>
+      </c>
+      <c r="Q311" s="5" t="n">
+        <v>-0.240145</v>
       </c>
     </row>
     <row r="312">
@@ -31757,15 +31819,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
+          <t>Weighted average number of common shares outstanding –</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -31808,26 +31874,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M312" s="5" t="n">
-        <v>-0.664621</v>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N312" s="5" t="n">
-        <v>-0.294999</v>
-      </c>
-      <c r="O312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>42.257899</v>
+      </c>
+      <c r="O312" s="5" t="n">
+        <v>4.948485</v>
+      </c>
+      <c r="P312" s="5" t="n">
+        <v>5.426321</v>
+      </c>
+      <c r="Q312" s="5" t="n">
+        <v>6.196736</v>
       </c>
     </row>
     <row r="313">
@@ -31836,15 +31898,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>basic and diluted</t>
+        </is>
+      </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Basic and fully diluted loss per share $</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -31887,26 +31953,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M313" s="5" t="n">
-        <v>36.407108</v>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N313" s="5" t="n">
-        <v>42.257899</v>
-      </c>
-      <c r="O313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="O313" s="5" t="n">
+        <v>-2e-07</v>
+      </c>
+      <c r="P313" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="Q313" s="5" t="n">
+        <v>-4e-08</v>
       </c>
     </row>
     <row r="314">
@@ -31917,19 +31979,15 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>outstanding – basic and diluted</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Basic and fully diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -31970,16 +32028,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M314" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="N314" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="O314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O314" s="5" t="n">
+        <v>0.551368</v>
       </c>
       <c r="P314" t="inlineStr">
         <is>
@@ -32000,19 +32060,15 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>(in United States Dollars)</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Sales $</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Settlement of flow through shares</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -32043,8 +32099,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K315" s="5" t="n">
-        <v>2.388321</v>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -32066,10 +32124,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P315" s="5" t="n">
+        <v>0.066</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -32085,17 +32141,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>(in United States Dollars)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Cost of Sales</t>
+          <t>Listing and filing fees $</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -32128,28 +32184,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K316" s="5" t="n">
-        <v>1.943354</v>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M316" s="5" t="n">
+        <v>0.013974</v>
+      </c>
+      <c r="N316" s="5" t="n">
+        <v>0.012903</v>
+      </c>
+      <c r="O316" s="5" t="n">
+        <v>0.015832</v>
       </c>
       <c r="P316" t="inlineStr">
         <is>
@@ -32170,15 +32222,19 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>(in United States Dollars)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>(in United States Dollars) total</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>Management and consulting fees (note 6)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -32209,28 +32265,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K317" s="5" t="n">
-        <v>0.444967</v>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M317" s="5" t="n">
+        <v>0.132188</v>
+      </c>
+      <c r="N317" s="5" t="n">
+        <v>0.074494</v>
+      </c>
+      <c r="O317" s="5" t="n">
+        <v>0.06660000000000001</v>
       </c>
       <c r="P317" t="inlineStr">
         <is>
@@ -32256,7 +32308,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Bad debt expense $</t>
+          <t>Share-based compensation (note 4)</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -32290,8 +32342,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K318" s="5" t="n">
-        <v>0.008399999999999999</v>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -32308,10 +32362,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O318" s="5" t="n">
+        <v>0.551368</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>
@@ -32332,19 +32384,15 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Impairment of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -32380,18 +32428,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L319" s="5" t="n">
-        <v>0.007606</v>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N319" s="5" t="n">
+        <v>-0.114781</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -32415,19 +32463,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 9)</t>
+          <t>Loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -32460,21 +32504,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K320" s="5" t="n">
-        <v>0.099484</v>
-      </c>
-      <c r="L320" s="5" t="n">
-        <v>0.049463</v>
-      </c>
-      <c r="M320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M320" s="5" t="n">
+        <v>-0.664621</v>
+      </c>
+      <c r="N320" s="5" t="n">
+        <v>-0.294999</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -32498,19 +32542,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -32518,36 +32558,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F321" s="5" t="n">
-        <v>0.008325000000000001</v>
-      </c>
-      <c r="G321" s="5" t="n">
-        <v>0.115297</v>
-      </c>
-      <c r="H321" s="5" t="n">
-        <v>0.113958</v>
-      </c>
-      <c r="I321" s="5" t="n">
-        <v>0.116075</v>
-      </c>
-      <c r="J321" s="5" t="n">
-        <v>0.113036</v>
-      </c>
-      <c r="K321" s="5" t="n">
-        <v>0.070101</v>
-      </c>
-      <c r="L321" s="5" t="n">
-        <v>0.049428</v>
-      </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M321" s="5" t="n">
+        <v>36.407108</v>
+      </c>
+      <c r="N321" s="5" t="n">
+        <v>42.257899</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -32573,15 +32623,19 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
+          <t>Basic and fully diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -32617,18 +32671,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L322" s="5" t="n">
-        <v>0.037658</v>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M322" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="N322" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -32654,17 +32706,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>(in United States Dollars)</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Sales $</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -32672,26 +32724,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F323" s="5" t="n">
-        <v>0.007627</v>
-      </c>
-      <c r="G323" s="5" t="n">
-        <v>0.076289</v>
-      </c>
-      <c r="H323" s="5" t="n">
-        <v>0.094892</v>
-      </c>
-      <c r="I323" s="5" t="n">
-        <v>0.09653200000000001</v>
-      </c>
-      <c r="J323" s="5" t="n">
-        <v>0.029632</v>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K323" s="5" t="n">
-        <v>0.004885</v>
-      </c>
-      <c r="L323" s="5" t="n">
-        <v>0.006741</v>
+        <v>2.388321</v>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
@@ -32727,15 +32791,19 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>(in United States Dollars)</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Warranty provision</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Cost of Sales</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -32756,14 +32824,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I324" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="J324" s="5" t="n">
-        <v>-0.015</v>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K324" s="5" t="n">
-        <v>0.025</v>
+        <v>1.943354</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -32804,44 +32876,52 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>(in United States Dollars)</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>(in United States Dollars) total</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F325" s="5" t="n">
-        <v>0.648388</v>
-      </c>
-      <c r="G325" s="5" t="n">
-        <v>0.99468</v>
-      </c>
-      <c r="H325" s="5" t="n">
-        <v>1.795021</v>
-      </c>
-      <c r="I325" s="5" t="n">
-        <v>1.631108</v>
-      </c>
-      <c r="J325" s="5" t="n">
-        <v>1.31441</v>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K325" s="5" t="n">
-        <v>0.259195</v>
-      </c>
-      <c r="L325" s="5" t="n">
-        <v>0.222404</v>
+        <v>0.444967</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
@@ -32882,14 +32962,10 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Net income (loss) from operations</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Bad debt expense $</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -32921,10 +32997,12 @@
         </is>
       </c>
       <c r="K326" s="5" t="n">
-        <v>0.185772</v>
-      </c>
-      <c r="L326" s="5" t="n">
-        <v>-0.222404</v>
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
@@ -32965,12 +33043,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -33003,11 +33081,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K327" s="5" t="n">
-        <v>-0.003251</v>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L327" s="5" t="n">
-        <v>-0.001859</v>
+        <v>0.007606</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
@@ -33048,10 +33128,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Write-off of inventory</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>Management and consulting fees (note 9)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -33082,13 +33166,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K328" s="5" t="n">
+        <v>0.099484</v>
       </c>
       <c r="L328" s="5" t="n">
-        <v>-0.023291</v>
+        <v>0.049463</v>
       </c>
       <c r="M328" t="inlineStr">
         <is>
@@ -33129,12 +33211,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Net income (loss) from continuing operations $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -33142,36 +33224,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F329" s="5" t="n">
+        <v>0.008325000000000001</v>
+      </c>
+      <c r="G329" s="5" t="n">
+        <v>0.115297</v>
+      </c>
+      <c r="H329" s="5" t="n">
+        <v>0.113958</v>
+      </c>
+      <c r="I329" s="5" t="n">
+        <v>0.116075</v>
+      </c>
+      <c r="J329" s="5" t="n">
+        <v>0.113036</v>
       </c>
       <c r="K329" s="5" t="n">
-        <v>0.182521</v>
+        <v>0.070101</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>-0.247554</v>
+        <v>0.049428</v>
       </c>
       <c r="M329" t="inlineStr">
         <is>
@@ -33212,7 +33284,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Loss from discontinued operations (note 13)</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -33246,13 +33318,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K330" s="5" t="n">
-        <v>-0.610975</v>
-      </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L330" s="5" t="n">
+        <v>0.037658</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
@@ -33293,47 +33365,39 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Gain on disposal of subsidiaries (note 13)</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F331" s="5" t="n">
+        <v>0.007627</v>
+      </c>
+      <c r="G331" s="5" t="n">
+        <v>0.076289</v>
+      </c>
+      <c r="H331" s="5" t="n">
+        <v>0.094892</v>
+      </c>
+      <c r="I331" s="5" t="n">
+        <v>0.09653200000000001</v>
+      </c>
+      <c r="J331" s="5" t="n">
+        <v>0.029632</v>
+      </c>
+      <c r="K331" s="5" t="n">
+        <v>0.004885</v>
       </c>
       <c r="L331" s="5" t="n">
-        <v>0.205776</v>
+        <v>0.006741</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
@@ -33374,14 +33438,10 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Warranty provision</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -33402,21 +33462,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I332" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J332" s="5" t="n">
+        <v>-0.015</v>
       </c>
       <c r="K332" s="5" t="n">
-        <v>-0.428454</v>
-      </c>
-      <c r="L332" s="5" t="n">
-        <v>-0.041778</v>
+        <v>0.025</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
@@ -33452,50 +33510,44 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Unrealized   foreign  exchange  gain   (loss)  on translation</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F333" s="5" t="n">
+        <v>0.648388</v>
+      </c>
+      <c r="G333" s="5" t="n">
+        <v>0.99468</v>
+      </c>
+      <c r="H333" s="5" t="n">
+        <v>1.795021</v>
+      </c>
+      <c r="I333" s="5" t="n">
+        <v>1.631108</v>
+      </c>
+      <c r="J333" s="5" t="n">
+        <v>1.31441</v>
       </c>
       <c r="K333" s="5" t="n">
-        <v>0.039717</v>
+        <v>0.259195</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>-0.000434</v>
+        <v>0.222404</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
@@ -33531,15 +33583,19 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>Net income (loss) from operations</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -33571,10 +33627,10 @@
         </is>
       </c>
       <c r="K334" s="5" t="n">
-        <v>-0.388737</v>
+        <v>0.185772</v>
       </c>
       <c r="L334" s="5" t="n">
-        <v>-0.042212</v>
+        <v>-0.222404</v>
       </c>
       <c r="M334" t="inlineStr">
         <is>
@@ -33610,15 +33666,19 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted (note 7)</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -33650,10 +33710,10 @@
         </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>3.678577</v>
+        <v>-0.003251</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>4.942378</v>
+        <v>-0.001859</v>
       </c>
       <c r="M335" t="inlineStr">
         <is>
@@ -33689,12 +33749,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Basic and fully diluted (loss) earnings per share from continuing operations (note 7) $</t>
+          <t>Write-off of inventory</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -33728,11 +33788,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K336" s="5" t="n">
-        <v>5e-08</v>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L336" s="5" t="n">
-        <v>-5e-08</v>
+        <v>-0.023291</v>
       </c>
       <c r="M336" t="inlineStr">
         <is>
@@ -33768,15 +33830,19 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Basic and fully diluted income (loss) earnings per share from discontinued operations (note 13) $</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>Net income (loss) from continuing operations $</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -33808,10 +33874,10 @@
         </is>
       </c>
       <c r="K337" s="5" t="n">
-        <v>-1.2e-07</v>
+        <v>0.182521</v>
       </c>
       <c r="L337" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.247554</v>
       </c>
       <c r="M337" t="inlineStr">
         <is>
@@ -33845,15 +33911,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Sales $</t>
+          <t>Loss from discontinued operations (note 13)</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -33866,20 +33936,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G338" s="5" t="n">
-        <v>4.002596</v>
-      </c>
-      <c r="H338" s="5" t="n">
-        <v>3.197803</v>
-      </c>
-      <c r="I338" s="5" t="n">
-        <v>2.056654</v>
-      </c>
-      <c r="J338" s="5" t="n">
-        <v>1.696782</v>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K338" s="5" t="n">
-        <v>2.494497</v>
+        <v>-0.610975</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -33918,17 +33996,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Gain on disposal of subsidiaries (note 13)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -33939,25 +34017,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G339" s="5" t="n">
-        <v>2.573861</v>
-      </c>
-      <c r="H339" s="5" t="n">
-        <v>2.217843</v>
-      </c>
-      <c r="I339" s="5" t="n">
-        <v>1.109974</v>
-      </c>
-      <c r="J339" s="5" t="n">
-        <v>1.396618</v>
-      </c>
-      <c r="K339" s="5" t="n">
-        <v>1.970926</v>
-      </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>0.205776</v>
       </c>
       <c r="M339" t="inlineStr">
         <is>
@@ -33991,15 +34077,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -34017,22 +34107,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H340" s="5" t="n">
-        <v>0.9799600000000001</v>
-      </c>
-      <c r="I340" s="5" t="n">
-        <v>0.94668</v>
-      </c>
-      <c r="J340" s="5" t="n">
-        <v>0.300164</v>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K340" s="5" t="n">
-        <v>0.523571</v>
-      </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.428454</v>
+      </c>
+      <c r="L340" s="5" t="n">
+        <v>-0.041778</v>
       </c>
       <c r="M340" t="inlineStr">
         <is>
@@ -34068,19 +34162,15 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Depreciation (note 4)</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Unrealized   foreign  exchange  gain   (loss)  on translation</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -34096,22 +34186,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H341" s="5" t="n">
-        <v>0.051014</v>
-      </c>
-      <c r="I341" s="5" t="n">
-        <v>0.060955</v>
-      </c>
-      <c r="J341" s="5" t="n">
-        <v>0.014145</v>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K341" s="5" t="n">
-        <v>0.004622</v>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.039717</v>
+      </c>
+      <c r="L341" s="5" t="n">
+        <v>-0.000434</v>
       </c>
       <c r="M341" t="inlineStr">
         <is>
@@ -34147,12 +34241,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Share-based payments (note 5(b))</t>
+          <t>Comprehensive loss $</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -34171,24 +34265,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H342" s="5" t="n">
-        <v>0.378717</v>
-      </c>
-      <c r="I342" s="5" t="n">
-        <v>0.034165</v>
-      </c>
-      <c r="J342" s="5" t="n">
-        <v>0.155891</v>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K342" s="5" t="n">
+        <v>-0.388737</v>
+      </c>
+      <c r="L342" s="5" t="n">
+        <v>-0.042212</v>
       </c>
       <c r="M342" t="inlineStr">
         <is>
@@ -34224,19 +34320,15 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 10)</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding – basic and diluted (note 7)</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -34252,22 +34344,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H343" s="5" t="n">
-        <v>0.775682</v>
-      </c>
-      <c r="I343" s="5" t="n">
-        <v>0.394304</v>
-      </c>
-      <c r="J343" s="5" t="n">
-        <v>0.497256</v>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K343" s="5" t="n">
-        <v>0.259484</v>
-      </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.678577</v>
+      </c>
+      <c r="L343" s="5" t="n">
+        <v>4.942378</v>
       </c>
       <c r="M343" t="inlineStr">
         <is>
@@ -34303,46 +34399,50 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Research and development</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Basic and fully diluted (loss) earnings per share from continuing operations (note 7) $</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F344" s="5" t="n">
-        <v>0.051038</v>
-      </c>
-      <c r="G344" s="5" t="n">
-        <v>0.077587</v>
-      </c>
-      <c r="H344" s="5" t="n">
-        <v>0.035164</v>
-      </c>
-      <c r="I344" s="5" t="n">
-        <v>0.08487699999999999</v>
-      </c>
-      <c r="J344" s="5" t="n">
-        <v>0.028944</v>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K344" s="5" t="n">
-        <v>0.043375</v>
-      </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-08</v>
+      </c>
+      <c r="L344" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="M344" t="inlineStr">
         <is>
@@ -34378,12 +34478,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Unrealized   foreign  exchange  gain   (loss)  on</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bad debt expense (note 8)</t>
+          <t>Basic and fully diluted income (loss) earnings per share from discontinued operations (note 13) $</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -34412,16 +34512,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J345" s="5" t="n">
-        <v>0.0033</v>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K345" s="5" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.2e-07</v>
+      </c>
+      <c r="L345" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="M345" t="inlineStr">
         <is>
@@ -34455,19 +34555,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Salaries and wages</t>
+          <t>Sales $</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>SalariesAndWages</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -34481,19 +34577,19 @@
         </is>
       </c>
       <c r="G346" s="5" t="n">
-        <v>0.002094</v>
+        <v>4.002596</v>
       </c>
       <c r="H346" s="5" t="n">
-        <v>0.184262</v>
+        <v>3.197803</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>0.548938</v>
+        <v>2.056654</v>
       </c>
       <c r="J346" s="5" t="n">
-        <v>0.331788</v>
+        <v>1.696782</v>
       </c>
       <c r="K346" s="5" t="n">
-        <v>0.297979</v>
+        <v>2.494497</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -34532,19 +34628,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -34557,22 +34649,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G347" s="5" t="n">
+        <v>2.573861</v>
       </c>
       <c r="H347" s="5" t="n">
-        <v>-0.815061</v>
+        <v>2.217843</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>-0.684428</v>
+        <v>1.109974</v>
       </c>
       <c r="J347" s="5" t="n">
-        <v>-1.014246</v>
+        <v>1.396618</v>
       </c>
       <c r="K347" s="5" t="n">
-        <v>-0.368495</v>
+        <v>1.970926</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -34611,17 +34701,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Foreign exchange expense</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -34637,21 +34727,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H348" s="5" t="n">
+        <v>0.9799600000000001</v>
+      </c>
+      <c r="I348" s="5" t="n">
+        <v>0.94668</v>
       </c>
       <c r="J348" s="5" t="n">
-        <v>0.005449</v>
+        <v>0.300164</v>
       </c>
       <c r="K348" s="5" t="n">
-        <v>-0.059959</v>
+        <v>0.523571</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -34697,34 +34783,40 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Other income – interest</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
+          <t>Depreciation (note 4)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F349" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="G349" s="5" t="n">
-        <v>0.000294</v>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H349" s="5" t="n">
-        <v>0.000293</v>
+        <v>0.051014</v>
       </c>
       <c r="I349" s="5" t="n">
-        <v>0.006748</v>
+        <v>0.060955</v>
       </c>
       <c r="J349" s="5" t="n">
-        <v>0.007656</v>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014145</v>
+      </c>
+      <c r="K349" s="5" t="n">
+        <v>0.004622</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -34770,14 +34862,10 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Share-based payments (note 5(b))</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -34788,20 +34876,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G350" s="5" t="n">
-        <v>-0.761548</v>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H350" s="5" t="n">
-        <v>-0.814768</v>
+        <v>0.378717</v>
       </c>
       <c r="I350" s="5" t="n">
-        <v>-0.6776799999999999</v>
+        <v>0.034165</v>
       </c>
       <c r="J350" s="5" t="n">
-        <v>-1.012039</v>
-      </c>
-      <c r="K350" s="5" t="n">
-        <v>-0.428454</v>
+        <v>0.155891</v>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -34847,10 +34939,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Tax expense (note 9)</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr"/>
+          <t>Management and consulting fees (note 10)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -34867,18 +34963,16 @@
         </is>
       </c>
       <c r="H351" s="5" t="n">
-        <v>-0.023963</v>
+        <v>0.775682</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>-0.015</v>
+        <v>0.394304</v>
       </c>
       <c r="J351" s="5" t="n">
-        <v>0.018042</v>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.497256</v>
+      </c>
+      <c r="K351" s="5" t="n">
+        <v>0.259484</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -34924,12 +35018,12 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Research and development</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -34937,31 +35031,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F352" s="5" t="n">
+        <v>0.051038</v>
+      </c>
+      <c r="G352" s="5" t="n">
+        <v>0.077587</v>
+      </c>
+      <c r="H352" s="5" t="n">
+        <v>0.035164</v>
+      </c>
+      <c r="I352" s="5" t="n">
+        <v>0.08487699999999999</v>
       </c>
       <c r="J352" s="5" t="n">
-        <v>-0.993997</v>
+        <v>0.028944</v>
       </c>
       <c r="K352" s="5" t="n">
-        <v>-0.428454</v>
+        <v>0.043375</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -35002,12 +35088,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange (loss) gain on translation</t>
+          <t>Bad debt expense (note 8)</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -35037,10 +35123,10 @@
         </is>
       </c>
       <c r="J353" s="5" t="n">
-        <v>-0.002321</v>
+        <v>0.0033</v>
       </c>
       <c r="K353" s="5" t="n">
-        <v>0.039717</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -35081,15 +35167,19 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Total comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>Salaries and wages</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -35101,19 +35191,19 @@
         </is>
       </c>
       <c r="G354" s="5" t="n">
-        <v>-0.861435</v>
+        <v>0.002094</v>
       </c>
       <c r="H354" s="5" t="n">
-        <v>-0.857536</v>
+        <v>0.184262</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>-0.682867</v>
+        <v>0.548938</v>
       </c>
       <c r="J354" s="5" t="n">
-        <v>-0.996318</v>
+        <v>0.331788</v>
       </c>
       <c r="K354" s="5" t="n">
-        <v>-0.388737</v>
+        <v>0.297979</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -35154,15 +35244,19 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted (note 6)</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -35178,21 +35272,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H355" s="5" t="n">
+        <v>-0.815061</v>
+      </c>
+      <c r="I355" s="5" t="n">
+        <v>-0.684428</v>
       </c>
       <c r="J355" s="5" t="n">
-        <v>32.236815</v>
+        <v>-1.014246</v>
       </c>
       <c r="K355" s="5" t="n">
-        <v>36.785774</v>
+        <v>-0.368495</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -35233,19 +35323,15 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Basic and fully diluted loss per share (note 6) $</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Foreign exchange expense</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -35261,17 +35347,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H356" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="I356" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J356" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.005449</v>
       </c>
       <c r="K356" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.059959</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -35317,7 +35407,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Bad debt expense</t>
+          <t>Other income – interest</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -35326,26 +35416,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F357" s="5" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="G357" s="5" t="n">
+        <v>0.000294</v>
+      </c>
+      <c r="H357" s="5" t="n">
+        <v>0.000293</v>
       </c>
       <c r="I357" s="5" t="n">
-        <v>0.02067</v>
+        <v>0.006748</v>
       </c>
       <c r="J357" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.007656</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
@@ -35396,12 +35480,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Total expense</t>
+          <t>Loss before income taxes</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -35414,26 +35498,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G358" s="5" t="n">
+        <v>-0.761548</v>
+      </c>
+      <c r="H358" s="5" t="n">
+        <v>-0.814768</v>
       </c>
       <c r="I358" s="5" t="n">
-        <v>1.631108</v>
+        <v>-0.6776799999999999</v>
       </c>
       <c r="J358" s="5" t="n">
-        <v>1.319859</v>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.012039</v>
+      </c>
+      <c r="K358" s="5" t="n">
+        <v>-0.428454</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -35479,7 +35557,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Net loss attributable to the common shareholders</t>
+          <t>Tax expense (note 9)</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -35499,13 +35577,13 @@
         </is>
       </c>
       <c r="H359" s="5" t="n">
-        <v>-0.838731</v>
+        <v>-0.023963</v>
       </c>
       <c r="I359" s="5" t="n">
-        <v>-0.69268</v>
+        <v>-0.015</v>
       </c>
       <c r="J359" s="5" t="n">
-        <v>-0.993997</v>
+        <v>0.018042</v>
       </c>
       <c r="K359" t="inlineStr">
         <is>
@@ -35551,15 +35629,19 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange (loss) gain on translation of foreign operations</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -35580,16 +35662,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I360" s="5" t="n">
-        <v>0.009813000000000001</v>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J360" s="5" t="n">
-        <v>-0.002321</v>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.993997</v>
+      </c>
+      <c r="K360" s="5" t="n">
+        <v>-0.428454</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -35635,7 +35717,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted (note 5)</t>
+          <t>Unrealized foreign exchange (loss) gain on translation</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -35649,22 +35731,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G361" s="5" t="n">
-        <v>3.870497</v>
-      </c>
-      <c r="H361" s="5" t="n">
-        <v>27.949448</v>
-      </c>
-      <c r="I361" s="5" t="n">
-        <v>32.236815</v>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J361" s="5" t="n">
-        <v>32.236815</v>
-      </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002321</v>
+      </c>
+      <c r="K361" s="5" t="n">
+        <v>0.039717</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -35710,7 +35796,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange (loss) gain on translation of Novateqni</t>
+          <t>Total comprehensive loss $</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -35724,26 +35810,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G362" s="5" t="n">
+        <v>-0.861435</v>
       </c>
       <c r="H362" s="5" t="n">
-        <v>-0.018805</v>
+        <v>-0.857536</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>0.009813000000000001</v>
-      </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.682867</v>
+      </c>
+      <c r="J362" s="5" t="n">
+        <v>-0.996318</v>
+      </c>
+      <c r="K362" s="5" t="n">
+        <v>-0.388737</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -35784,19 +35864,15 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Depreciation (note 3)</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding – basic and diluted (note 6)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -35807,26 +35883,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G363" s="5" t="n">
-        <v>0.000745</v>
-      </c>
-      <c r="H363" s="5" t="n">
-        <v>0.051014</v>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J363" s="5" t="n">
+        <v>32.236815</v>
+      </c>
+      <c r="K363" s="5" t="n">
+        <v>36.785774</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -35867,15 +35943,19 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Share-based payments (note 4 (b))</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr"/>
+          <t>Basic and fully diluted loss per share (note 6) $</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -35892,22 +35972,16 @@
         </is>
       </c>
       <c r="H364" s="5" t="n">
-        <v>0.378717</v>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="I364" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J364" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="K364" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -35953,37 +36027,35 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 8)</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Bad debt expense</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F365" s="5" t="n">
-        <v>0.574611</v>
-      </c>
-      <c r="G365" s="5" t="n">
-        <v>0.691181</v>
-      </c>
-      <c r="H365" s="5" t="n">
-        <v>0.775682</v>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I365" s="5" t="n">
+        <v>0.02067</v>
+      </c>
+      <c r="J365" s="5" t="n">
+        <v>0.0033</v>
       </c>
       <c r="K365" t="inlineStr">
         <is>
@@ -36034,10 +36106,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>(Loss) Income before other income and listing costs</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr"/>
+          <t>Total expense</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -36048,21 +36124,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G366" s="5" t="n">
-        <v>0.434055</v>
-      </c>
-      <c r="H366" s="5" t="n">
-        <v>-0.815061</v>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I366" s="5" t="n">
+        <v>1.631108</v>
+      </c>
+      <c r="J366" s="5" t="n">
+        <v>1.319859</v>
       </c>
       <c r="K366" t="inlineStr">
         <is>
@@ -36113,7 +36189,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Listing costs (note 1)</t>
+          <t>Net loss attributable to the common shareholders</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -36127,23 +36203,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G367" s="5" t="n">
-        <v>-1.195897</v>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H367" s="5" t="n">
+        <v>-0.838731</v>
+      </c>
+      <c r="I367" s="5" t="n">
+        <v>-0.69268</v>
+      </c>
+      <c r="J367" s="5" t="n">
+        <v>-0.993997</v>
       </c>
       <c r="K367" t="inlineStr">
         <is>
@@ -36189,12 +36261,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Tax expense (note 7)</t>
+          <t>Unrealized foreign exchange (loss) gain on translation of foreign operations</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -36208,21 +36280,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G368" s="5" t="n">
-        <v>-0.091806</v>
-      </c>
-      <c r="H368" s="5" t="n">
-        <v>-0.023963</v>
-      </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I368" s="5" t="n">
+        <v>0.009813000000000001</v>
+      </c>
+      <c r="J368" s="5" t="n">
+        <v>-0.002321</v>
       </c>
       <c r="K368" t="inlineStr">
         <is>
@@ -36268,12 +36340,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Net loss to the common shareholders</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted (note 5)</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -36288,20 +36360,16 @@
         </is>
       </c>
       <c r="G369" s="5" t="n">
-        <v>-0.8533539999999999</v>
+        <v>3.870497</v>
       </c>
       <c r="H369" s="5" t="n">
-        <v>-0.838731</v>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>27.949448</v>
+      </c>
+      <c r="I369" s="5" t="n">
+        <v>32.236815</v>
+      </c>
+      <c r="J369" s="5" t="n">
+        <v>32.236815</v>
       </c>
       <c r="K369" t="inlineStr">
         <is>
@@ -36352,7 +36420,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange loss on translation of Novateqni</t>
+          <t>Unrealized foreign exchange (loss) gain on translation of Novateqni</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -36366,16 +36434,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G370" s="5" t="n">
-        <v>-0.008081</v>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H370" s="5" t="n">
         <v>-0.018805</v>
       </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I370" s="5" t="n">
+        <v>0.009813000000000001</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
@@ -36426,17 +36494,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Basic and fully diluted loss per share (note 5) $</t>
+          <t>Depreciation (note 3)</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -36450,10 +36518,10 @@
         </is>
       </c>
       <c r="G371" s="5" t="n">
-        <v>-2.2e-07</v>
+        <v>0.000745</v>
       </c>
       <c r="H371" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.051014</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -36509,34 +36577,32 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>INCOME (LOSS)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Sales $</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Share-based payments (note 4 (b))</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F372" s="5" t="n">
-        <v>3.145871</v>
-      </c>
-      <c r="G372" s="5" t="n">
-        <v>4.002596</v>
-      </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H372" s="5" t="n">
+        <v>0.378717</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -36592,17 +36658,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>INCOME (LOSS)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Management and consulting fees (note 8)</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -36611,15 +36677,13 @@
         </is>
       </c>
       <c r="F373" s="5" t="n">
-        <v>2.173941</v>
+        <v>0.574611</v>
       </c>
       <c r="G373" s="5" t="n">
-        <v>2.573861</v>
-      </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.691181</v>
+      </c>
+      <c r="H373" s="5" t="n">
+        <v>0.775682</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -36675,12 +36739,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>INCOME (LOSS)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) total</t>
+          <t>(Loss) Income before other income and listing costs</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -36689,16 +36753,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F374" s="5" t="n">
-        <v>0.97193</v>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G374" s="5" t="n">
-        <v>1.428735</v>
-      </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.434055</v>
+      </c>
+      <c r="H374" s="5" t="n">
+        <v>-0.815061</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -36759,14 +36823,10 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Listing costs (note 1)</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -36778,7 +36838,7 @@
         </is>
       </c>
       <c r="G375" s="5" t="n">
-        <v>0.000745</v>
+        <v>-1.195897</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
@@ -36844,7 +36904,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Income before other income and listing costs</t>
+          <t>Tax expense (note 7)</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -36853,16 +36913,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F376" s="5" t="n">
-        <v>0.323542</v>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G376" s="5" t="n">
-        <v>0.434055</v>
-      </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.091806</v>
+      </c>
+      <c r="H376" s="5" t="n">
+        <v>-0.023963</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -36923,29 +36983,25 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>(Loss) income before income taxes</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Net loss to the common shareholders</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F377" s="5" t="n">
-        <v>0.323544</v>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G377" s="5" t="n">
-        <v>-0.761548</v>
-      </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.8533539999999999</v>
+      </c>
+      <c r="H377" s="5" t="n">
+        <v>-0.838731</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -37001,34 +37057,30 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Income tax expense (note 7)</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Unrealized foreign exchange loss on translation of Novateqni</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F378" s="5" t="n">
-        <v>-0.053385</v>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G378" s="5" t="n">
-        <v>-0.091806</v>
-      </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008081</v>
+      </c>
+      <c r="H378" s="5" t="n">
+        <v>-0.018805</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -37084,30 +37136,34 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Net (loss) income to the common shareholders</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>Basic and fully diluted loss per share (note 5) $</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F379" s="5" t="n">
-        <v>0.270159</v>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G379" s="5" t="n">
-        <v>-0.8533539999999999</v>
-      </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.2e-07</v>
+      </c>
+      <c r="H379" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
@@ -37163,27 +37219,29 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Other comprehensive (loss) income</t>
+          <t>INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange loss on translation of Hombre</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
+          <t>Sales $</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F380" s="5" t="n">
+        <v>3.145871</v>
       </c>
       <c r="G380" s="5" t="n">
-        <v>-0.008081</v>
+        <v>4.002596</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
@@ -37244,25 +37302,29 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Other comprehensive (loss) income</t>
+          <t>INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Total comprehensive (loss) income $</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F381" s="5" t="n">
-        <v>0.270159</v>
+        <v>2.173941</v>
       </c>
       <c r="G381" s="5" t="n">
-        <v>-0.861435</v>
+        <v>2.573861</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
@@ -37323,12 +37385,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Other comprehensive (loss) income</t>
+          <t>INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted (note 5)</t>
+          <t>INCOME (LOSS) total</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -37338,10 +37400,10 @@
         </is>
       </c>
       <c r="F382" s="5" t="n">
-        <v>0.001</v>
+        <v>0.97193</v>
       </c>
       <c r="G382" s="5" t="n">
-        <v>3.870497</v>
+        <v>1.428735</v>
       </c>
       <c r="H382" t="inlineStr">
         <is>
@@ -37402,25 +37464,31 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Other comprehensive (loss) income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Basic and fully diluted (loss) earnings per share (note 5) $</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F383" s="5" t="n">
-        <v>0.00027</v>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G383" s="5" t="n">
-        <v>-2.2e-07</v>
+        <v>0.000745</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
@@ -37481,25 +37549,25 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Incorporation on July</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>EXPENSES December 31, 2013 December</t>
+          <t>Income before other income and listing costs</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
-      <c r="E384" s="5" t="n">
-        <v>0.002012</v>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F384" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.323542</v>
+      </c>
+      <c r="G384" s="5" t="n">
+        <v>0.434055</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
@@ -37560,29 +37628,29 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Incorporation on July</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Office $</t>
+          <t>(Loss) income before income taxes</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E385" s="5" t="n">
-        <v>0.000943</v>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F385" s="5" t="n">
-        <v>0.004855</v>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.323544</v>
+      </c>
+      <c r="G385" s="5" t="n">
+        <v>-0.761548</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
@@ -37643,29 +37711,29 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Incorporation on July</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Income tax expense (note 7)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E386" s="5" t="n">
-        <v>0.0065</v>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F386" s="5" t="n">
-        <v>0.028447</v>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.053385</v>
+      </c>
+      <c r="G386" s="5" t="n">
+        <v>-0.091806</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
@@ -37726,29 +37794,25 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Incorporation on July</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E387" s="5" t="n">
-        <v>0.001804</v>
+          <t>Net (loss) income to the common shareholders</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F387" s="5" t="n">
-        <v>0.007177</v>
-      </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.270159</v>
+      </c>
+      <c r="G387" s="5" t="n">
+        <v>-0.8533539999999999</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -37809,27 +37873,27 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Incorporation on July</t>
+          <t>Other comprehensive (loss) income</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Incorporation costs</t>
+          <t>Unrealized foreign exchange loss on translation of Hombre</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
-      <c r="E388" s="5" t="n">
-        <v>0.000347</v>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G388" s="5" t="n">
+        <v>-0.008081</v>
       </c>
       <c r="H388" t="inlineStr">
         <is>
@@ -37890,31 +37954,25 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Incorporation on July</t>
+          <t>Other comprehensive (loss) income</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Total comprehensive (loss) income $</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F389" s="5" t="n">
-        <v>0.001323</v>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.270159</v>
+      </c>
+      <c r="G389" s="5" t="n">
+        <v>-0.861435</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
@@ -37975,29 +38033,25 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Incorporation on July</t>
+          <t>Other comprehensive (loss) income</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Operating loss</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E390" s="5" t="n">
-        <v>-0.009594</v>
+          <t>Weighted average number of common shares outstanding – basic and diluted (note 5)</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F390" s="5" t="n">
-        <v>-0.041802</v>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001</v>
+      </c>
+      <c r="G390" s="5" t="n">
+        <v>3.870497</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
@@ -38058,31 +38112,25 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Incorporation on July</t>
+          <t>Other comprehensive (loss) income</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Basic and fully diluted (loss) earnings per share (note 5) $</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F391" s="5" t="n">
-        <v>0.002717</v>
-      </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00027</v>
+      </c>
+      <c r="G391" s="5" t="n">
+        <v>-2.2e-07</v>
       </c>
       <c r="H391" t="inlineStr">
         <is>
@@ -38148,19 +38196,15 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>EXPENSES December 31, 2013 December</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
       <c r="E392" s="5" t="n">
-        <v>-0.009594</v>
+        <v>0.002012</v>
       </c>
       <c r="F392" s="5" t="n">
-        <v>-0.039085</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
@@ -38231,19 +38275,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (Note 3(g)) $</t>
+          <t>Office $</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E393" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.000943</v>
       </c>
       <c r="F393" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.004855</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
@@ -38314,15 +38358,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Weighted average number of Class A shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E394" s="5" t="n">
-        <v>1.840065</v>
+        <v>0.0065</v>
       </c>
       <c r="F394" s="5" t="n">
-        <v>7.638356</v>
+        <v>0.028447</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>
@@ -38393,15 +38441,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>For the Year ended December</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>Transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E395" s="5" t="n">
-        <v>0.002013</v>
+        <v>0.001804</v>
       </c>
       <c r="F395" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.007177</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
@@ -38467,20 +38519,22 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Class A Shares    Share Capital     Surplus      Deficit         Total</t>
+          <t>Incorporation on July</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Balance December 31, 2012 2,000,000 $ 100,000 $ - $</t>
+          <t>Incorporation costs</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
       <c r="E396" s="5" t="n">
-        <v>0.090406</v>
-      </c>
-      <c r="F396" s="5" t="n">
-        <v>-0.009594</v>
+        <v>0.000347</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -38546,22 +38600,26 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Shares  issued  for  cash,  net  of  share</t>
+          <t>Incorporation on July</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Shares  issued  for  cash,  net  of  share issuance costs (Note 4) 6,000,000 426,265 -</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr"/>
-      <c r="E397" s="5" t="n">
-        <v>0.426265</v>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F397" s="5" t="n">
+        <v>0.001323</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -38627,22 +38685,24 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Shares  issued  for  cash,  net  of  share</t>
+          <t>Incorporation on July</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Stock options issued (Note 4) - - 31,488</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>Operating loss</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E398" s="5" t="n">
-        <v>0.031488</v>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.009594</v>
+      </c>
+      <c r="F398" s="5" t="n">
+        <v>-0.041802</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -38708,24 +38768,26 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Shares  issued  for  cash,  net  of  share</t>
+          <t>Incorporation on July</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Loss for the period - - -</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E399" s="5" t="n">
-        <v>-0.039085</v>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F399" s="5" t="n">
-        <v>-0.039085</v>
+        <v>0.002717</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -38791,20 +38853,24 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Shares  issued  for  cash,  net  of  share</t>
+          <t>Incorporation on July</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>For Period from Incorporation on July 31, 2012 to December</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E400" s="5" t="n">
-        <v>0.002012</v>
+        <v>-0.009594</v>
       </c>
       <c r="F400" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.039085</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -38870,24 +38936,24 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Class A Shares    Share Capital     Surplus      Deficit          Total</t>
+          <t>Incorporation on July</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Balance July 31, 2012 - $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr"/>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted loss per share (Note 3(g)) $</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E401" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F401" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -38953,22 +39019,20 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Class A Shares    Share Capital     Surplus      Deficit          Total</t>
+          <t>Incorporation on July</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Shares issued for cash (Note 4) 2,000,000 100,000 -</t>
+          <t>Weighted average number of Class A shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
       <c r="E402" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.840065</v>
+      </c>
+      <c r="F402" s="5" t="n">
+        <v>7.638356</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -39034,24 +39098,20 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Class A Shares    Share Capital     Surplus      Deficit          Total</t>
+          <t>Incorporation on July</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>For the Year ended December</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
       <c r="E403" s="5" t="n">
-        <v>-0.009594</v>
+        <v>0.002013</v>
       </c>
       <c r="F403" s="5" t="n">
-        <v>-0.009594</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -39117,7 +39177,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Class A Shares    Share Capital     Surplus      Deficit          Total</t>
+          <t>Class A Shares    Share Capital     Surplus      Deficit         Total</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -39196,21 +39256,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares  issued  for  cash,  net  of  share</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Office $</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Shares  issued  for  cash,  net  of  share issuance costs (Note 4) 6,000,000 426,265 -</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
       <c r="E405" s="5" t="n">
-        <v>0.000943</v>
+        <v>0.426265</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39281,21 +39337,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares  issued  for  cash,  net  of  share</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Stock options issued (Note 4) - - 31,488</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
       <c r="E406" s="5" t="n">
-        <v>0.0065</v>
+        <v>0.031488</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39366,26 +39418,24 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares  issued  for  cash,  net  of  share</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
+          <t>Loss for the period - - -</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E407" s="5" t="n">
-        <v>0.001804</v>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.039085</v>
+      </c>
+      <c r="F407" s="5" t="n">
+        <v>-0.039085</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
@@ -39451,22 +39501,20 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares  issued  for  cash,  net  of  share</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Incorporation costs</t>
+          <t>For Period from Incorporation on July 31, 2012 to December</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" s="5" t="n">
-        <v>0.000347</v>
-      </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002012</v>
+      </c>
+      <c r="F408" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
@@ -39532,21 +39580,19 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Class A Shares    Share Capital     Surplus      Deficit          Total</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E409" s="5" t="n">
-        <v>0.009594</v>
+          <t>Balance July 31, 2012 - $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39617,21 +39663,17 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Class A Shares    Share Capital     Surplus      Deficit          Total</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued for cash (Note 4) 2,000,000 100,000 -</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" s="5" t="n">
-        <v>-0.009594</v>
+        <v>0.1</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39702,26 +39744,24 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Class A Shares    Share Capital     Surplus      Deficit          Total</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (note 3(g)) $</t>
+          <t>Loss for the period - - -</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E411" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.009594</v>
+      </c>
+      <c r="F411" s="5" t="n">
+        <v>-0.009594</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
@@ -39787,26 +39827,20 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Class A Shares    Share Capital     Surplus      Deficit          Total</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Weighted average number of Class A shares outstanding</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Balance December 31, 2012 2,000,000 $ 100,000 $ - $</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" s="5" t="n">
-        <v>1.840065</v>
-      </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.090406</v>
+      </c>
+      <c r="F412" s="5" t="n">
+        <v>-0.009594</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -39872,19 +39906,21 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Shares       Capital        Deficit        Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2012 - $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office $</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E413" s="5" t="n">
+        <v>0.000943</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -39955,17 +39991,21 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Shares       Capital        Deficit        Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Shares issued for cash (note 4) 2,000,000 100,000 -</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E414" s="5" t="n">
-        <v>0.1</v>
+        <v>0.0065</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40036,17 +40076,21 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Shares       Capital        Deficit        Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Loss for the period - - (9,594)</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>Transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E415" s="5" t="n">
-        <v>-0.009594</v>
+        <v>0.001804</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40117,74 +40161,740 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Shares       Capital        Deficit        Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Balance December 31, 2012 2,000,000 $ 100,000 $ (9,594) $</t>
+          <t>Incorporation costs</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" s="5" t="n">
+        <v>0.000347</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E417" s="5" t="n">
+        <v>0.009594</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E418" s="5" t="n">
+        <v>-0.009594</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (note 3(g)) $</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E419" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Weighted average number of Class A shares outstanding</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E420" s="5" t="n">
+        <v>1.840065</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Shares       Capital        Deficit        Total</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2012 - $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Shares       Capital        Deficit        Total</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Shares issued for cash (note 4) 2,000,000 100,000 -</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Shares       Capital        Deficit        Total</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Loss for the period - - (9,594)</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" s="5" t="n">
+        <v>-0.009594</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Shares       Capital        Deficit        Total</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Balance December 31, 2012 2,000,000 $ 100,000 $ (9,594) $</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" s="5" t="n">
         <v>0.090406</v>
       </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q416" t="inlineStr">
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
         <is>
           <t>-</t>
         </is>
